--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,12 +1218,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GIS24EXP-2573</t>
+          <t>GIS24EXP-2527</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Переезд БД дева</t>
+          <t>Авторизация КЛУ (REST) Изменения в БД</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1235,12 +1235,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GIS24EXP-738</t>
+          <t>GIS24EXP-2573</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Прод. ЭПД. Формирование отчетов на</t>
+          <t>Переезд БД дева</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SUPASISP-231</t>
+          <t>GIS24EXP-738</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SQL. ПФУ. Сгенерировать ТС до актуальной</t>
+          <t>Прод. ЭПД. Формирование отчетов на</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1269,12 +1269,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SUPASISP-261</t>
+          <t>SUPASISP-231</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Test. ПМУ ПФУ. Реестр. ТехКарта</t>
+          <t>SQL. ПФУ. Сгенерировать ТС до актуальной</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1286,12 +1286,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SUPASISP-281</t>
+          <t>SUPASISP-261</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SQL. ПМУ / ПФУ. Портал. Реестр. Оптимизировать SQL выгрузки</t>
+          <t>Test. ПМУ ПФУ. Реестр. ТехКарта</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1303,12 +1303,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SUPASISP-350</t>
+          <t>SUPASISP-281</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ДЕВ. ПМУ / ПФУ. Реестр ТС. Выгрузка реестра тс, некорректные</t>
+          <t>SQL. ПМУ / ПФУ. Портал. Реестр. Оптимизировать SQL выгрузки</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1320,12 +1320,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SUPASISP-405</t>
+          <t>SUPASISP-350</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SQL. ПМУ / ПФУ. Исправить справочники</t>
+          <t>ДЕВ. ПМУ / ПФУ. Реестр ТС. Выгрузка реестра тс, некорректные</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1337,12 +1337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SUPASISP-440</t>
+          <t>SUPASISP-405</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SQL. ПМУ / ПФУ. Убрать округление времени из всех функций</t>
+          <t>SQL. ПМУ / ПФУ. Исправить справочники</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1354,15 +1354,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>SUPASISP-440</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SQL. ПМУ / ПФУ. Убрать округление времени из всех функций</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>10.03.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>SUPASISP-66</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>ПФУ. Портал. Главная . Виджеты. Виджет " въезд ) выезд" + Виджет</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>10.03.2025</t>
         </is>
